--- a/docs/Shopify_Deal_Workbook.xlsx
+++ b/docs/Shopify_Deal_Workbook.xlsx
@@ -23,12 +23,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="$#,##0;($#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.0&quot;x&quot;;(0.0&quot;x&quot;);&quot;-&quot;"/>
     <numFmt numFmtId="168" formatCode="$#,##0.0;($#,##0.0);&quot;-&quot;"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0;(#,##0.0);&quot;-&quot;"/>
+    <numFmt numFmtId="170" formatCode="0.00%;(0.00%);&quot;-&quot;"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -164,7 +166,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -302,11 +304,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <right/>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -497,6 +505,36 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="11" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="11" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="10" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="9" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="9" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -893,7 +931,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="74" t="inlineStr">
         <is>
           <t>Workbook Navigation</t>
         </is>
@@ -1038,7 +1076,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="74" t="inlineStr">
         <is>
           <t>Investment Summary</t>
         </is>
@@ -1093,7 +1131,7 @@
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Mkt cap ~$141B less net cash ~$5.7B</t>
+          <t>Mkt cap ~$141B less net cash ~$6.3B (FY25 + Q1 FCF)</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1194,12 @@
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>$14,885M</t>
+          <t>$14,818M</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Street consensus: GS, JPM, Baird, Citizens, KeyBanc</t>
+          <t>Model FY2026E consensus; GS/JPM/Baird buildup</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1211,12 @@
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>~18.7%</t>
+          <t>~18.8%</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Consensus range: 18.3%–19.1%</t>
+          <t>Model: ~$2,790M EBITDA on $14,818M revenue</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1245,12 @@
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>~1.50x</t>
+          <t>~1.58x</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>38x–45x FY2028E EBITDA of ~$4.5B</t>
+          <t>45x FY2028E EBITDA $4.7B + $12.4B net cash (model)</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1272,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="74" t="inlineStr">
         <is>
           <t>Color Coding</t>
         </is>
@@ -1399,7 +1437,7 @@
       <c r="C2" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="74" t="inlineStr">
         <is>
           <t>Company &amp; Deal</t>
         </is>
@@ -1487,7 +1525,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="74" t="inlineStr">
         <is>
           <t>Entry Assumptions (at $108/share — May 2026)</t>
         </is>
@@ -1509,21 +1547,21 @@
     <row r="15">
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>Entry Revenue ($M)   [FY2026E consensus]</t>
+          <t>Entry Revenue ($M)   [FY2026E, model]</t>
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>14885</v>
+        <v>14818</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>Entry EBITDA ($M)   [FY2026E, 18.7% adj.]</t>
+          <t>Entry EBITDA ($M)   [FY2026E, 18.8% adj.]</t>
         </is>
       </c>
       <c r="C16" s="25" t="n">
-        <v>2785</v>
+        <v>2790</v>
       </c>
     </row>
     <row r="17">
@@ -1533,7 +1571,7 @@
         </is>
       </c>
       <c r="C17" s="26" t="n">
-        <v>0.187</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="18">
@@ -1560,11 +1598,11 @@
     <row r="20">
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>Net Debt at Entry ($M)  [net cash = neg]</t>
+          <t>Net Debt at Entry ($M)  [net cash: FY25 + Q1'26 FCF]</t>
         </is>
       </c>
       <c r="C20" s="25" t="n">
-        <v>-5700</v>
+        <v>-6254</v>
       </c>
     </row>
     <row r="21">
@@ -1579,7 +1617,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="74" t="inlineStr">
         <is>
           <t>Exit Assumptions (FY2028E Base Case)</t>
         </is>
@@ -1601,21 +1639,21 @@
     <row r="25">
       <c r="B25" s="22" t="inlineStr">
         <is>
-          <t>Exit Revenue ($M)  [FY2028E, ~22% YoY]</t>
+          <t>Exit Revenue ($M)  [FY2028E, model]</t>
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>22450</v>
+        <v>22138</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="22" t="inlineStr">
         <is>
-          <t>Exit EBITDA ($M)  [FY2028E, ~20% margin]</t>
+          <t>Exit EBITDA ($M)  [FY2028E, ~21.2% margin]</t>
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>4490</v>
+        <v>4687</v>
       </c>
     </row>
     <row r="27">
@@ -1634,18 +1672,19 @@
           <t>Exit EV ($M)  [=EBITDA × Multiple]</t>
         </is>
       </c>
-      <c r="C28" s="25" t="n">
-        <v>202050</v>
+      <c r="C28" s="75">
+        <f>C26*C27</f>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="22" t="inlineStr">
         <is>
-          <t>Net Debt at Exit ($M)  [growing net cash]</t>
+          <t>Net Debt at Exit ($M)  [model cash $12.4B, $0 debt]</t>
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>-8500</v>
+        <v>-12369</v>
       </c>
     </row>
     <row r="30">
@@ -1654,12 +1693,13 @@
           <t>Proceeds to Equity ($M)  [=Exit EV − Net Debt]</t>
         </is>
       </c>
-      <c r="C30" s="25" t="n">
-        <v>210550</v>
+      <c r="C30" s="75">
+        <f>C28-C29</f>
+        <v/>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="74" t="inlineStr">
         <is>
           <t>Returns Summary</t>
         </is>
@@ -1712,7 +1752,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="74" t="inlineStr">
         <is>
           <t>NTB Registry — Need-to-Believe Statements</t>
         </is>
@@ -1902,7 +1942,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="74" t="inlineStr">
         <is>
           <t>INCOME STATEMENT</t>
         </is>
@@ -1918,16 +1958,16 @@
           <t>Revenue ($M)</t>
         </is>
       </c>
-      <c r="C8" s="25" t="n">
-        <v>5595</v>
-      </c>
-      <c r="D8" s="25" t="n">
-        <v>7061</v>
-      </c>
-      <c r="E8" s="25" t="n">
-        <v>8884</v>
-      </c>
-      <c r="F8" s="25" t="n">
+      <c r="C8" s="75" t="n">
+        <v>5600</v>
+      </c>
+      <c r="D8" s="75" t="n">
+        <v>7060</v>
+      </c>
+      <c r="E8" s="75" t="n">
+        <v>8880</v>
+      </c>
+      <c r="F8" s="75" t="n">
         <v>11556</v>
       </c>
       <c r="G8" s="35" t="inlineStr">
@@ -2128,17 +2168,17 @@
           <t>EBITDA (adj.) ($M)</t>
         </is>
       </c>
-      <c r="C17" s="37" t="n">
-        <v>222</v>
-      </c>
-      <c r="D17" s="37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E17" s="37" t="n">
-        <v>1583</v>
-      </c>
-      <c r="F17" s="37" t="n">
-        <v>2010</v>
+      <c r="C17" s="76" t="n">
+        <v>44</v>
+      </c>
+      <c r="D17" s="76" t="n">
+        <v>813</v>
+      </c>
+      <c r="E17" s="76" t="n">
+        <v>1509</v>
+      </c>
+      <c r="F17" s="76" t="n">
+        <v>1996</v>
       </c>
       <c r="G17" s="35" t="inlineStr">
         <is>
@@ -2152,17 +2192,17 @@
           <t xml:space="preserve">  EBITDA Margin %</t>
         </is>
       </c>
-      <c r="C18" s="26" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="D18" s="26" t="n">
-        <v>0.142</v>
-      </c>
-      <c r="E18" s="26" t="n">
-        <v>0.178</v>
-      </c>
-      <c r="F18" s="26" t="n">
-        <v>0.174</v>
+      <c r="C18" s="77" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="D18" s="77" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="E18" s="77" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F18" s="77" t="n">
+        <v>0.173</v>
       </c>
       <c r="G18" s="35" t="inlineStr"/>
     </row>
@@ -2307,7 +2347,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="74" t="inlineStr">
         <is>
           <t>BALANCE SHEET (KEY ITEMS)</t>
         </is>
@@ -2323,17 +2363,17 @@
           <t>Cash &amp; Equivalents ($M)</t>
         </is>
       </c>
-      <c r="C27" s="25" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D27" s="25" t="n">
-        <v>5500</v>
-      </c>
-      <c r="E27" s="25" t="n">
-        <v>6200</v>
-      </c>
-      <c r="F27" s="25" t="n">
-        <v>7900</v>
+      <c r="C27" s="75" t="n">
+        <v>5053</v>
+      </c>
+      <c r="D27" s="75" t="n">
+        <v>5008</v>
+      </c>
+      <c r="E27" s="75" t="n">
+        <v>5479</v>
+      </c>
+      <c r="F27" s="75" t="n">
+        <v>5778</v>
       </c>
       <c r="G27" s="35" t="inlineStr">
         <is>
@@ -2347,21 +2387,21 @@
           <t>Total Debt ($M)</t>
         </is>
       </c>
-      <c r="C28" s="25" t="n">
-        <v>921</v>
-      </c>
-      <c r="D28" s="25" t="n">
-        <v>921</v>
-      </c>
-      <c r="E28" s="25" t="n">
-        <v>921</v>
-      </c>
-      <c r="F28" s="25" t="n">
-        <v>921</v>
+      <c r="C28" s="75" t="n">
+        <v>913</v>
+      </c>
+      <c r="D28" s="75" t="n">
+        <v>916</v>
+      </c>
+      <c r="E28" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="75" t="n">
+        <v>0</v>
       </c>
       <c r="G28" s="35" t="inlineStr">
         <is>
-          <t>$921M notes; no revolving credit drawn</t>
+          <t>$913M conv. notes repaid FY2024; $0 thereafter</t>
         </is>
       </c>
     </row>
@@ -2371,17 +2411,17 @@
           <t>Net Debt ($M) [neg = net cash]</t>
         </is>
       </c>
-      <c r="C29" s="25" t="n">
-        <v>-4079</v>
-      </c>
-      <c r="D29" s="25" t="n">
-        <v>-4579</v>
-      </c>
-      <c r="E29" s="25" t="n">
-        <v>-5279</v>
-      </c>
-      <c r="F29" s="25" t="n">
-        <v>-6979</v>
+      <c r="C29" s="75" t="n">
+        <v>-4140</v>
+      </c>
+      <c r="D29" s="75" t="n">
+        <v>-4092</v>
+      </c>
+      <c r="E29" s="75" t="n">
+        <v>-5479</v>
+      </c>
+      <c r="F29" s="75" t="n">
+        <v>-5778</v>
       </c>
       <c r="G29" s="35" t="inlineStr">
         <is>
@@ -2414,7 +2454,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="74" t="inlineStr">
         <is>
           <t>CASH FLOW (KEY ITEMS)</t>
         </is>
@@ -2430,17 +2470,17 @@
           <t>Operating Cash Flow ($M)</t>
         </is>
       </c>
-      <c r="C33" s="25" t="n">
-        <v>378</v>
-      </c>
-      <c r="D33" s="25" t="n">
-        <v>1035</v>
-      </c>
-      <c r="E33" s="25" t="n">
-        <v>1690</v>
-      </c>
-      <c r="F33" s="25" t="n">
-        <v>2207</v>
+      <c r="C33" s="75" t="n">
+        <v>-136</v>
+      </c>
+      <c r="D33" s="75" t="n">
+        <v>944</v>
+      </c>
+      <c r="E33" s="75" t="n">
+        <v>1616</v>
+      </c>
+      <c r="F33" s="75" t="n">
+        <v>2033</v>
       </c>
       <c r="G33" s="35" t="inlineStr">
         <is>
@@ -2454,17 +2494,17 @@
           <t>Capex ($M)</t>
         </is>
       </c>
-      <c r="C34" s="25" t="n">
-        <v>100</v>
-      </c>
-      <c r="D34" s="25" t="n">
-        <v>130</v>
-      </c>
-      <c r="E34" s="25" t="n">
-        <v>160</v>
-      </c>
-      <c r="F34" s="25" t="n">
-        <v>200</v>
+      <c r="C34" s="75" t="n">
+        <v>50</v>
+      </c>
+      <c r="D34" s="75" t="n">
+        <v>39</v>
+      </c>
+      <c r="E34" s="75" t="n">
+        <v>19</v>
+      </c>
+      <c r="F34" s="75" t="n">
+        <v>26</v>
       </c>
       <c r="G34" s="35" t="inlineStr">
         <is>
@@ -2478,21 +2518,21 @@
           <t>Free Cash Flow ($M)</t>
         </is>
       </c>
-      <c r="C35" s="37" t="n">
-        <v>278</v>
-      </c>
-      <c r="D35" s="37" t="n">
+      <c r="C35" s="76" t="n">
+        <v>-186</v>
+      </c>
+      <c r="D35" s="76" t="n">
         <v>905</v>
       </c>
-      <c r="E35" s="37" t="n">
-        <v>1530</v>
-      </c>
-      <c r="F35" s="37" t="n">
+      <c r="E35" s="76" t="n">
+        <v>1597</v>
+      </c>
+      <c r="F35" s="76" t="n">
         <v>2007</v>
       </c>
       <c r="G35" s="35" t="inlineStr">
         <is>
-          <t>FCF = OCF - Capex; FY2025A $2,007M (17.4% margin) per Q1'26 release</t>
+          <t>FCF = OCF - Capex; FY2022: -$186M (growth investment); FY2025A $2,007M (17.4%)</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2646,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="74" t="inlineStr">
         <is>
           <t>Projection Assumptions (Yellow = change for scenario analysis)</t>
         </is>
@@ -2639,19 +2679,21 @@
       <c r="E7" s="39" t="inlineStr"/>
       <c r="F7" s="39" t="inlineStr"/>
       <c r="G7" s="26" t="n">
-        <v>0.29</v>
+        <v>0.282</v>
       </c>
       <c r="H7" s="26" t="n">
-        <v>0.24</v>
+        <v>0.232</v>
       </c>
       <c r="I7" s="26" t="n">
-        <v>0.22</v>
+        <v>0.212</v>
       </c>
       <c r="J7" s="26" t="n">
         <v>0.2</v>
       </c>
-      <c r="K7" s="26" t="n">
-        <v>0.18</v>
+      <c r="K7" s="26" t="inlineStr">
+        <is>
+          <t>FY2026E: +28.2% (model); decel to +18% by FY2030E</t>
+        </is>
       </c>
       <c r="L7" s="35" t="inlineStr">
         <is>
@@ -2877,7 +2919,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="74" t="inlineStr">
         <is>
           <t>Income Statement</t>
         </is>
@@ -3232,17 +3274,17 @@
           <t>EBITDA (adj.)</t>
         </is>
       </c>
-      <c r="C25" s="44" t="n">
-        <v>222</v>
-      </c>
-      <c r="D25" s="44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E25" s="44" t="n">
-        <v>1583</v>
-      </c>
-      <c r="F25" s="44" t="n">
-        <v>2010</v>
+      <c r="C25" s="76" t="n">
+        <v>44</v>
+      </c>
+      <c r="D25" s="76" t="n">
+        <v>813</v>
+      </c>
+      <c r="E25" s="76" t="n">
+        <v>1509</v>
+      </c>
+      <c r="F25" s="76" t="n">
+        <v>1996</v>
       </c>
       <c r="G25" s="45">
         <f>G19-G24</f>
@@ -3260,9 +3302,10 @@
         <f>J19-J24</f>
         <v/>
       </c>
-      <c r="K25" s="45">
-        <f>K19-K24</f>
-        <v/>
+      <c r="K25" s="45" t="inlineStr">
+        <is>
+          <t>FY2025A 17.3% (model); FY2026E ~18.8%; FY2028E ~21.2%</t>
+        </is>
       </c>
       <c r="L25" s="35" t="inlineStr">
         <is>
@@ -3276,17 +3319,17 @@
           <t xml:space="preserve">  EBITDA Margin %</t>
         </is>
       </c>
-      <c r="C26" s="42" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="D26" s="42" t="n">
-        <v>0.142</v>
-      </c>
-      <c r="E26" s="42" t="n">
-        <v>0.178</v>
-      </c>
-      <c r="F26" s="42" t="n">
-        <v>0.174</v>
+      <c r="C26" s="78" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="D26" s="78" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="E26" s="78" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F26" s="78" t="n">
+        <v>0.173</v>
       </c>
       <c r="G26" s="43">
         <f>IFERROR(G25/G17,"-")</f>
@@ -3544,7 +3587,7 @@
       <c r="L32" s="35" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="74" t="inlineStr">
         <is>
           <t>Free Cash Flow</t>
         </is>
@@ -3597,17 +3640,17 @@
           <t>Less: Capex</t>
         </is>
       </c>
-      <c r="C36" s="40" t="n">
-        <v>100</v>
-      </c>
-      <c r="D36" s="40" t="n">
-        <v>130</v>
-      </c>
-      <c r="E36" s="40" t="n">
-        <v>160</v>
-      </c>
-      <c r="F36" s="40" t="n">
-        <v>200</v>
+      <c r="C36" s="79" t="n">
+        <v>50</v>
+      </c>
+      <c r="D36" s="79" t="n">
+        <v>39</v>
+      </c>
+      <c r="E36" s="79" t="n">
+        <v>19</v>
+      </c>
+      <c r="F36" s="79" t="n">
+        <v>26</v>
       </c>
       <c r="G36" s="41">
         <f>G17*G14</f>
@@ -3662,16 +3705,16 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="C38" s="44" t="n">
-        <v>278</v>
-      </c>
-      <c r="D38" s="44" t="n">
+      <c r="C38" s="76" t="n">
+        <v>-186</v>
+      </c>
+      <c r="D38" s="76" t="n">
         <v>905</v>
       </c>
-      <c r="E38" s="44" t="n">
-        <v>1530</v>
-      </c>
-      <c r="F38" s="44" t="n">
+      <c r="E38" s="76" t="n">
+        <v>1597</v>
+      </c>
+      <c r="F38" s="76" t="n">
         <v>2007</v>
       </c>
       <c r="G38" s="45">
@@ -3690,9 +3733,10 @@
         <f>J25-J36-J37</f>
         <v/>
       </c>
-      <c r="K38" s="45">
-        <f>K25-K36-K37</f>
-        <v/>
+      <c r="K38" s="45" t="inlineStr">
+        <is>
+          <t>FY2022: -$186M; FY2025A $2,007M (17.4%); FY2028E $4,274M (19.3%)</t>
+        </is>
       </c>
       <c r="L38" s="35" t="inlineStr">
         <is>
@@ -3701,7 +3745,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" s="74" t="inlineStr">
         <is>
           <t>Shopify-Specific KPIs (Supplemental)</t>
         </is>
@@ -3722,32 +3766,34 @@
           <t>GMV ($B)</t>
         </is>
       </c>
-      <c r="C41" s="47" t="n">
-        <v>197</v>
-      </c>
-      <c r="D41" s="47" t="n">
-        <v>236</v>
-      </c>
-      <c r="E41" s="47" t="n">
-        <v>282</v>
-      </c>
-      <c r="F41" s="47" t="n">
-        <v>329</v>
-      </c>
-      <c r="G41" s="47" t="n">
-        <v>489</v>
-      </c>
-      <c r="H41" s="47" t="n">
-        <v>597</v>
-      </c>
-      <c r="I41" s="47" t="n">
-        <v>726</v>
+      <c r="C41" s="80" t="n">
+        <v>197.3</v>
+      </c>
+      <c r="D41" s="80" t="n">
+        <v>235.9</v>
+      </c>
+      <c r="E41" s="80" t="n">
+        <v>292.3</v>
+      </c>
+      <c r="F41" s="80" t="n">
+        <v>378.4</v>
+      </c>
+      <c r="G41" s="80" t="n">
+        <v>477.8</v>
+      </c>
+      <c r="H41" s="80" t="n">
+        <v>583</v>
+      </c>
+      <c r="I41" s="80" t="n">
+        <v>699.6</v>
       </c>
       <c r="J41" s="47" t="n">
         <v>871</v>
       </c>
-      <c r="K41" s="47" t="n">
-        <v>1027</v>
+      <c r="K41" s="47" t="inlineStr">
+        <is>
+          <t>Model FY2025A $378.4B (+29% YoY); FY2028E $699.6B (+20%)</t>
+        </is>
       </c>
       <c r="L41" s="35" t="inlineStr">
         <is>
@@ -3761,28 +3807,34 @@
           <t>GPV Penetration % of GMV</t>
         </is>
       </c>
-      <c r="C42" s="26" t="n"/>
-      <c r="D42" s="26" t="n"/>
-      <c r="E42" s="26" t="n">
+      <c r="C42" s="77" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="D42" s="77" t="n">
         <v>0.6</v>
       </c>
-      <c r="F42" s="26" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="G42" s="26" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="H42" s="26" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I42" s="26" t="n">
-        <v>0.72</v>
+      <c r="E42" s="77" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="F42" s="77" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G42" s="77" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H42" s="77" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I42" s="77" t="n">
+        <v>0.79</v>
       </c>
       <c r="J42" s="26" t="n">
         <v>0.73</v>
       </c>
-      <c r="K42" s="26" t="n">
-        <v>0.74</v>
+      <c r="K42" s="26" t="inlineStr">
+        <is>
+          <t>GPV% FY2025A: 68%; FY2026E: 71%; FY2028E: 79% (model)</t>
+        </is>
       </c>
       <c r="L42" s="35" t="inlineStr">
         <is>
@@ -3796,28 +3848,34 @@
           <t>Merchant Solutions Rev/GMV (Take Rate)</t>
         </is>
       </c>
-      <c r="C43" s="26" t="n"/>
-      <c r="D43" s="26" t="n"/>
-      <c r="E43" s="26" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="F43" s="26" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="G43" s="26" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="H43" s="26" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="I43" s="26" t="n">
-        <v>0.0245</v>
+      <c r="C43" s="81" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="D43" s="81" t="n">
+        <v>0.0221</v>
+      </c>
+      <c r="E43" s="81" t="n">
+        <v>0.0223</v>
+      </c>
+      <c r="F43" s="81" t="n">
+        <v>0.0233</v>
+      </c>
+      <c r="G43" s="81" t="n">
+        <v>0.0241</v>
+      </c>
+      <c r="H43" s="81" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="I43" s="81" t="n">
+        <v>0.0259</v>
       </c>
       <c r="J43" s="26" t="n">
         <v>0.025</v>
       </c>
-      <c r="K43" s="26" t="n">
-        <v>0.025</v>
+      <c r="K43" s="26" t="inlineStr">
+        <is>
+          <t>Attach rate FY2025A: 2.33%; FY2028E: 2.59% (model)</t>
+        </is>
       </c>
       <c r="L43" s="35" t="inlineStr">
         <is>
@@ -3831,28 +3889,34 @@
           <t>MRR ($M)</t>
         </is>
       </c>
-      <c r="C44" s="47" t="n"/>
-      <c r="D44" s="47" t="n"/>
-      <c r="E44" s="47" t="n">
-        <v>182</v>
-      </c>
-      <c r="F44" s="47" t="n">
-        <v>200</v>
-      </c>
-      <c r="G44" s="47" t="n">
-        <v>212</v>
-      </c>
-      <c r="H44" s="47" t="n">
-        <v>248</v>
-      </c>
-      <c r="I44" s="47" t="n">
+      <c r="C44" s="75" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="D44" s="75" t="n">
+        <v>144</v>
+      </c>
+      <c r="E44" s="75" t="n">
+        <v>178</v>
+      </c>
+      <c r="F44" s="75" t="n">
+        <v>205</v>
+      </c>
+      <c r="G44" s="75" t="n">
+        <v>239</v>
+      </c>
+      <c r="H44" s="75" t="n">
+        <v>267</v>
+      </c>
+      <c r="I44" s="75" t="n">
         <v>291</v>
       </c>
       <c r="J44" s="47" t="n">
         <v>340</v>
       </c>
-      <c r="K44" s="47" t="n">
-        <v>397</v>
+      <c r="K44" s="47" t="inlineStr">
+        <is>
+          <t>MRR FY2025A: $205M; FY2026E: $239M; FY2028E: $291M (model)</t>
+        </is>
       </c>
       <c r="L44" s="35" t="inlineStr">
         <is>
@@ -5308,11 +5372,11 @@
           <t>Quarterly</t>
         </is>
       </c>
-      <c r="G7" s="25" t="n">
-        <v>489</v>
-      </c>
-      <c r="H7" s="25" t="n">
-        <v>329</v>
+      <c r="G7" s="82" t="n">
+        <v>477.8</v>
+      </c>
+      <c r="H7" s="80" t="n">
+        <v>378.4</v>
       </c>
       <c r="I7" s="28">
         <f>IFERROR(H7-G7,"-")</f>
@@ -5354,7 +5418,7 @@
         </is>
       </c>
       <c r="G8" s="25" t="n">
-        <v>14885</v>
+        <v>14818</v>
       </c>
       <c r="H8" s="25" t="n">
         <v>11556</v>
@@ -5489,10 +5553,10 @@
         </is>
       </c>
       <c r="G11" s="25" t="n">
-        <v>248</v>
-      </c>
-      <c r="H11" s="25" t="n">
-        <v>200</v>
+        <v>239</v>
+      </c>
+      <c r="H11" s="75" t="n">
+        <v>205</v>
       </c>
       <c r="I11" s="28">
         <f>IFERROR(H11-G11,"-")</f>
@@ -5669,10 +5733,10 @@
         </is>
       </c>
       <c r="G15" s="26" t="n">
-        <v>0.187</v>
-      </c>
-      <c r="H15" s="26" t="n">
-        <v>0.174</v>
+        <v>0.188</v>
+      </c>
+      <c r="H15" s="77" t="n">
+        <v>0.173</v>
       </c>
       <c r="I15" s="28">
         <f>IFERROR(H15-G15,"-")</f>
@@ -5886,10 +5950,10 @@
         </is>
       </c>
       <c r="G20" s="26" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H20" s="77" t="n">
         <v>0.68</v>
-      </c>
-      <c r="H20" s="26" t="n">
-        <v>0.64</v>
       </c>
       <c r="I20" s="28">
         <f>IFERROR(H20-G20,"-")</f>
@@ -5930,11 +5994,11 @@
           <t>Quarterly</t>
         </is>
       </c>
-      <c r="G21" s="26" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="H21" s="26" t="n">
-        <v>0.023</v>
+      <c r="G21" s="83" t="n">
+        <v>0.0241</v>
+      </c>
+      <c r="H21" s="81" t="n">
+        <v>0.0233</v>
       </c>
       <c r="I21" s="28">
         <f>IFERROR(H21-G21,"-")</f>
@@ -6062,7 +6126,7 @@
         </is>
       </c>
       <c r="G24" s="25" t="n">
-        <v>2610</v>
+        <v>2550</v>
       </c>
       <c r="H24" s="25" t="n">
         <v>2007</v>
@@ -6107,7 +6171,7 @@
         </is>
       </c>
       <c r="G25" s="26" t="n">
-        <v>0.175</v>
+        <v>0.172</v>
       </c>
       <c r="H25" s="26" t="n">
         <v>0.174</v>
